--- a/site/StructureDefinition-hcen-document-reference.xlsx
+++ b/site/StructureDefinition-hcen-document-reference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3647" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="598">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -300,7 +300,10 @@
 </t>
   </si>
   <si>
-    <t>ID lógico de este artefacto.</t>
+    <t>Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
     <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
@@ -316,7 +319,10 @@
 </t>
   </si>
   <si>
-    <t>Metadatos sobre el recurso.</t>
+    <t>Metadata about the resource</t>
+  </si>
+  <si>
+    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -333,7 +339,10 @@
 </t>
   </si>
   <si>
-    <t>Conjunto de reglas bajo las cuales se creó este contenido.</t>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
@@ -349,7 +358,10 @@
 </t>
   </si>
   <si>
-    <t>Idioma del contenido del recurso.</t>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
   </si>
   <si>
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
@@ -378,7 +390,10 @@
 </t>
   </si>
   <si>
-    <t>Resumen del recurso en texto para interpretación humana.</t>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
     <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
@@ -401,7 +416,10 @@
 </t>
   </si>
   <si>
-    <t>Recursos integrados en línea (inline).</t>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
   </si>
   <si>
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
@@ -423,7 +441,10 @@
 </t>
   </si>
   <si>
-    <t>Contenido adicional definido por implementaciones.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -538,7 +559,21 @@
     <t>DocumentReference.modifierExtension</t>
   </si>
   <si>
-    <t>Extensiones que no pueden ser ignoradas.</t>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -635,7 +670,10 @@
     <t>DocumentReference.status</t>
   </si>
   <si>
-    <t>Estado de la referencia: current, superseded o entered-in-error.</t>
+    <t>current | superseded | entered-in-error</t>
+  </si>
+  <si>
+    <t>The status of this document reference.</t>
   </si>
   <si>
     <t>This is the status of the DocumentReference object, which might be independent from the docStatus element.
@@ -904,17 +942,10 @@
     <t>DocumentReference.author.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -1015,7 +1046,10 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t>Profesional, rol u organización que autentica legalmente el documento.</t>
+    <t>Who/what authenticated the document</t>
+  </si>
+  <si>
+    <t>Which person or organization authenticates that this document is valid.</t>
   </si>
   <si>
     <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
@@ -1046,7 +1080,10 @@
 </t>
   </si>
   <si>
-    <t>Organización responsable de custodiar el documento</t>
+    <t>Organization which maintains the document</t>
+  </si>
+  <si>
+    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
   </si>
   <si>
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
@@ -1100,9 +1137,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
@@ -1137,7 +1171,10 @@
 </t>
   </si>
   <si>
-    <t>Documento objetivo de la relación.</t>
+    <t>Target of the relationship</t>
+  </si>
+  <si>
+    <t>The target document of this relationship.</t>
   </si>
   <si>
     <t>Composition.relatesTo.target</t>
@@ -1174,7 +1211,10 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Descripción legible del documento.</t>
+    <t>Human-readable description</t>
+  </si>
+  <si>
+    <t>Human-readable description of the source document.</t>
   </si>
   <si>
     <t>What the document is about,  a terse summary of the document.</t>
@@ -1195,7 +1235,10 @@
     <t>DocumentReference.securityLabel</t>
   </si>
   <si>
-    <t>Etiquetas de seguridad y confidencialidad del documento.</t>
+    <t>Document security-tags</t>
+  </si>
+  <si>
+    <t>A set of Security-Tag codes specifying the level of privacy/security of the Document. Note that DocumentReference.meta.security contains the security labels of the "reference" to the document, while DocumentReference.securityLabel contains a snapshot of the security labels on the document the reference refers to.</t>
   </si>
   <si>
     <t>The confidentiality codes can carry multiple vocabulary items. HL7 has developed an understanding of security and privacy tags that might be desirable in a Document Sharing environment, called HL7 Healthcare Privacy and Security Classification System (HCS). The following specification is recommended but not mandated, as the vocabulary bindings are an administrative domain responsibility. The use of this method is up to the policy domain such as the XDS Affinity Domain or other Trust Domain where all parties including sender and recipients are trusted to appropriately tag and enforce.   
@@ -1226,7 +1269,10 @@
     <t>DocumentReference.content</t>
   </si>
   <si>
-    <t>El documento referenciado.</t>
+    <t>Document referenced</t>
+  </si>
+  <si>
+    <t>The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
   </si>
   <si>
     <t>Bundle(Composition+*)</t>
@@ -1251,7 +1297,10 @@
 </t>
   </si>
   <si>
-    <t>Dónde acceder al documento (URL o Datos).</t>
+    <t>Where to access the document</t>
+  </si>
+  <si>
+    <t>The document or URL of the document along with critical metadata to prove content has integrity.</t>
   </si>
   <si>
     <t>Composition.language, 
@@ -1284,7 +1333,10 @@
 </t>
   </si>
   <si>
-    <t>Referencia al Binary que contiene el CDA del mismo documento.</t>
+    <t>Referencia al Binary del prestador que contiene el CDA XML.</t>
+  </si>
+  <si>
+    <t>En HCEN ITI-65, referencia al recurso FHIR HCENCdaBinary del prestador que contiene el CDA XML del mismo documento. La referencia informa la URL original recuperable del recurso Binary.</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.extension:binary.id</t>
@@ -1297,12 +1349,6 @@
   </si>
   <si>
     <t>DocumentReference.content.attachment.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.extension:binary.url</t>
@@ -1339,7 +1385,7 @@
     <t>ID del Recurso Binario</t>
   </si>
   <si>
-    <t>Referencia al recurso Binary que contiene la representación CDA del documento clínico.</t>
+    <t>Referencia al recurso FHIR Binary del prestador que contiene la representación CDA XML del documento clínico. En HCEN ITI-65 se informa la URL HTTP(S) absoluta original de ese recurso. La recuperación del CDA se realiza mediante la URL devuelta por HCEN ITI-67, según las reglas de HCEN ITI-68.</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1408,7 +1454,10 @@
     <t>DocumentReference.content.attachment.language</t>
   </si>
   <si>
-    <t>Idioma del contenido documental expresado mediante BCP-47.</t>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
   </si>
   <si>
     <t>Users need to be able to choose between the languages in a set of attachments.</t>
@@ -1430,7 +1479,10 @@
 </t>
   </si>
   <si>
-    <t>Datos en línea (base64).</t>
+    <t>Data inline, base64ed</t>
+  </si>
+  <si>
+    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
   </si>
   <si>
     <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
@@ -1455,7 +1507,10 @@
 </t>
   </si>
   <si>
-    <t>Referencia a la representación Bundle FHIR del documento.</t>
+    <t>URL original del Bundle FHIR del prestador en la publicación.</t>
+  </si>
+  <si>
+    <t>En HCEN ITI-65, URL HTTP(S) absoluta original del prestador para recuperar el Bundle documental FHIR. Es distinta del fullUrl de la entrada del envío y de la URL de recuperación que devuelve Plataforma en HCEN ITI-67.</t>
   </si>
   <si>
     <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
@@ -1519,7 +1574,10 @@
     <t>DocumentReference.content.attachment.title</t>
   </si>
   <si>
-    <t>Título del documento para su presentación.</t>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
   </si>
   <si>
     <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
@@ -1541,7 +1599,10 @@
 </t>
   </si>
   <si>
-    <t>Fecha y hora de creación del documento referenciado.</t>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
   </si>
   <si>
     <t>This is often tracked as an integrity issue for use of the attachment.</t>
@@ -1578,7 +1639,10 @@
     <t>DocumentReference.context</t>
   </si>
   <si>
-    <t>Contexto clínico del documento.</t>
+    <t>Clinical context of document</t>
+  </si>
+  <si>
+    <t>The clinical context in which the document was prepared.</t>
   </si>
   <si>
     <t>These values are primarily added to help with searching for interesting/relevant documents.</t>
@@ -1603,7 +1667,10 @@
 </t>
   </si>
   <si>
-    <t>Contexto (episodio/visita) del documento.</t>
+    <t>Context of the document  content</t>
+  </si>
+  <si>
+    <t>Describes the clinical encounter or type of care that the document content is associated with.</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1621,7 +1688,10 @@
     <t>DocumentReference.context.event</t>
   </si>
   <si>
-    <t>Actos clínicos principales documentados.</t>
+    <t>Main clinical acts documented</t>
+  </si>
+  <si>
+    <t>This list of codes represents the main clinical acts, such as a colonoscopy or an appendectomy, being documented. In some cases, the event is inherent in the type Code, such as a "History and Physical Report" in which the procedure being documented is necessarily a "History and Physical" act.</t>
   </si>
   <si>
     <t>An event can further specialize the act inherent in the type, such as  where it is simply "Procedure Report" and the procedure was a "colonoscopy". If one or more event codes are included, they shall not conflict with the values inherent in the class or type elements as such a conflict would create an ambiguous situation.</t>
@@ -1652,7 +1722,10 @@
 </t>
   </si>
   <si>
-    <t>Tiempo de servicio que está siendo documentado</t>
+    <t>Time of service that is being documented</t>
+  </si>
+  <si>
+    <t>The time period over which the service that is described by the document was provided.</t>
   </si>
   <si>
     <t>Composition.event.period</t>
@@ -1729,7 +1802,10 @@
     <t>DocumentReference.context.facilityType</t>
   </si>
   <si>
-    <t>Tipo de centro de salud donde se atendió al paciente.</t>
+    <t>Kind of facility where patient was seen</t>
+  </si>
+  <si>
+    <t>The kind of facility where the patient was seen.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
@@ -1768,7 +1844,10 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t>Datos del paciente tal como los informa el prestador de origen.</t>
+    <t>Patient demographics from source</t>
+  </si>
+  <si>
+    <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
   </si>
   <si>
     <t>DocumentEntry.sourcePatientInfo, DocumentEntry.sourcePatientId</t>
@@ -1781,7 +1860,10 @@
 </t>
   </si>
   <si>
-    <t>Identificadores o recursos relacionados con el documento.</t>
+    <t>Related identifiers or resources</t>
+  </si>
+  <si>
+    <t>Related identifiers or resources associated with the DocumentReference.</t>
   </si>
   <si>
     <t>May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
@@ -2448,10 +2530,10 @@
         <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2501,7 +2583,7 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -2539,10 +2621,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2565,13 +2647,13 @@
         <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2622,7 +2704,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -2634,7 +2716,7 @@
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2660,10 +2742,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2686,16 +2768,16 @@
         <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2745,7 +2827,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2757,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2783,10 +2865,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2809,16 +2891,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2844,13 +2926,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2868,7 +2950,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -2880,7 +2962,7 @@
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2906,14 +2988,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2932,16 +3014,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2991,7 +3073,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -3003,7 +3085,7 @@
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -3012,7 +3094,7 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>20</v>
@@ -3029,14 +3111,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3055,16 +3137,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3114,7 +3196,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3135,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>20</v>
@@ -3152,10 +3234,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3163,7 +3245,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>81</v>
@@ -3178,13 +3260,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3223,17 +3305,17 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3245,7 +3327,7 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3271,13 +3353,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
@@ -3299,13 +3381,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3356,7 +3438,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3365,10 +3447,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3394,13 +3476,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -3422,13 +3504,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3479,7 +3561,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3488,10 +3570,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3517,13 +3599,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -3545,13 +3627,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3602,7 +3684,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3611,10 +3693,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3640,13 +3722,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3668,13 +3750,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3725,7 +3807,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3734,10 +3816,10 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3763,13 +3845,13 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>20</v>
@@ -3791,13 +3873,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3848,7 +3930,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3857,10 +3939,10 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -3886,13 +3968,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
@@ -3914,13 +3996,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3971,7 +4053,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3980,10 +4062,10 @@
         <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -4009,13 +4091,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>20</v>
@@ -4037,13 +4119,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4094,7 +4176,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4103,10 +4185,10 @@
         <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -4132,14 +4214,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4158,16 +4240,20 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -4215,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4227,7 +4313,7 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -4236,7 +4322,7 @@
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
@@ -4253,10 +4339,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4279,19 +4365,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4340,7 +4426,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4352,36 +4438,36 @@
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4404,13 +4490,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4449,17 +4535,17 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4471,39 +4557,39 @@
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
@@ -4525,13 +4611,13 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4582,7 +4668,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4594,39 +4680,39 @@
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>20</v>
@@ -4648,13 +4734,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4705,7 +4791,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4717,36 +4803,36 @@
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4769,16 +4855,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4804,13 +4890,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4828,7 +4914,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -4840,36 +4926,36 @@
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4892,16 +4978,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4927,13 +5013,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4951,7 +5037,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4963,25 +5049,25 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>20</v>
@@ -4989,10 +5075,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5015,16 +5101,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5050,11 +5136,11 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -5072,7 +5158,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5084,40 +5170,40 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5136,16 +5222,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5171,11 +5257,11 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -5193,7 +5279,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5205,36 +5291,36 @@
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5257,13 +5343,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5314,7 +5400,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5326,40 +5412,40 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5378,16 +5464,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5437,7 +5523,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5449,22 +5535,22 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>20</v>
@@ -5475,10 +5561,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5501,16 +5587,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5548,17 +5634,17 @@
         <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5570,39 +5656,39 @@
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="B29" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="C29" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
@@ -5624,16 +5710,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5683,7 +5769,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5695,36 +5781,36 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5747,13 +5833,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5804,7 +5890,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5825,7 +5911,7 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5842,14 +5928,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5868,16 +5954,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5915,19 +6001,19 @@
         <v>20</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5939,7 +6025,7 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5948,7 +6034,7 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5965,10 +6051,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5991,16 +6077,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6050,7 +6136,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6059,10 +6145,10 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -6071,7 +6157,7 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -6088,10 +6174,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6114,16 +6200,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6149,13 +6235,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -6173,7 +6259,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6185,7 +6271,7 @@
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -6194,7 +6280,7 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -6211,10 +6297,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6237,16 +6323,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6296,7 +6382,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6308,7 +6394,7 @@
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -6317,7 +6403,7 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6334,10 +6420,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6360,16 +6446,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6419,7 +6505,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6431,7 +6517,7 @@
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -6440,7 +6526,7 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6457,10 +6543,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6483,16 +6569,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6542,7 +6628,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6554,36 +6640,36 @@
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6606,16 +6692,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6665,7 +6751,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6677,16 +6763,16 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6703,10 +6789,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6729,16 +6815,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6788,7 +6874,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6800,16 +6886,16 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6821,15 +6907,15 @@
         <v>20</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6852,13 +6938,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6909,7 +6995,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6930,7 +7016,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6947,14 +7033,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6973,16 +7059,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7032,7 +7118,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7044,7 +7130,7 @@
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -7053,7 +7139,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -7070,14 +7156,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7096,19 +7182,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>345</v>
+        <v>177</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7157,7 +7243,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7169,7 +7255,7 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -7178,7 +7264,7 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -7195,10 +7281,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7221,16 +7307,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7256,13 +7342,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -7280,7 +7366,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>90</v>
@@ -7292,16 +7378,16 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -7313,15 +7399,15 @@
         <v>20</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7344,13 +7430,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7401,7 +7487,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>90</v>
@@ -7413,16 +7499,16 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -7434,15 +7520,15 @@
         <v>20</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7465,13 +7551,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7522,7 +7608,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7543,7 +7629,7 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -7560,14 +7646,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7586,16 +7672,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7633,19 +7719,19 @@
         <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7657,7 +7743,7 @@
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7666,7 +7752,7 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7683,10 +7769,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7709,16 +7795,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7768,7 +7854,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7777,10 +7863,10 @@
         <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7789,7 +7875,7 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7806,10 +7892,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7832,16 +7918,16 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7867,13 +7953,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7891,7 +7977,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7903,7 +7989,7 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7912,7 +7998,7 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7929,10 +8015,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7955,16 +8041,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8014,7 +8100,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8026,7 +8112,7 @@
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -8035,7 +8121,7 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -8052,10 +8138,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8078,16 +8164,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8137,7 +8223,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8149,7 +8235,7 @@
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -8158,7 +8244,7 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -8175,10 +8261,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8201,19 +8287,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8262,7 +8348,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8274,7 +8360,7 @@
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8283,7 +8369,7 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -8292,18 +8378,18 @@
         <v>20</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8326,19 +8412,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8363,11 +8449,11 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8385,7 +8471,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8397,36 +8483,36 @@
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>384</v>
+        <v>398</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8449,13 +8535,13 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8506,7 +8592,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>90</v>
@@ -8518,16 +8604,16 @@
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -8544,10 +8630,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8570,13 +8656,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8627,7 +8713,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8648,7 +8734,7 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -8665,14 +8751,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8691,16 +8777,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8750,7 +8836,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8762,7 +8848,7 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8771,7 +8857,7 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8788,14 +8874,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8814,19 +8900,19 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>345</v>
+        <v>177</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8875,7 +8961,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8887,7 +8973,7 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8896,7 +8982,7 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8913,10 +8999,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8939,13 +9025,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8996,7 +9082,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>90</v>
@@ -9008,36 +9094,36 @@
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>398</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9060,13 +9146,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9117,7 +9203,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9138,7 +9224,7 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
@@ -9155,10 +9241,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9181,13 +9267,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9226,19 +9312,19 @@
         <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9250,7 +9336,7 @@
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -9276,13 +9362,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>20</v>
@@ -9304,13 +9390,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9361,7 +9447,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9373,7 +9459,7 @@
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9399,10 +9485,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9425,13 +9511,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9482,7 +9568,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9503,7 +9589,7 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>20</v>
@@ -9520,10 +9606,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9546,13 +9632,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
+        <v>137</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>410</v>
+        <v>138</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9591,19 +9677,19 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9615,7 +9701,7 @@
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9641,10 +9727,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9667,16 +9753,16 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9684,7 +9770,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>20</v>
@@ -9726,7 +9812,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>90</v>
@@ -9747,7 +9833,7 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>20</v>
@@ -9764,10 +9850,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9790,13 +9876,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9847,7 +9933,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9859,7 +9945,7 @@
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9868,7 +9954,7 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
@@ -9885,10 +9971,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9911,13 +9997,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9968,7 +10054,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9989,7 +10075,7 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -10006,14 +10092,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10032,16 +10118,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10079,19 +10165,19 @@
         <v>20</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10103,7 +10189,7 @@
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -10112,7 +10198,7 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
@@ -10129,10 +10215,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10155,16 +10241,16 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10214,7 +10300,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10223,10 +10309,10 @@
         <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10235,7 +10321,7 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>20</v>
@@ -10252,10 +10338,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10278,16 +10364,16 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10313,13 +10399,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -10337,7 +10423,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10349,7 +10435,7 @@
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -10358,7 +10444,7 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
@@ -10375,10 +10461,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10401,16 +10487,16 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10460,7 +10546,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10472,7 +10558,7 @@
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10481,7 +10567,7 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -10498,10 +10584,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10524,16 +10610,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10583,7 +10669,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10595,7 +10681,7 @@
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -10604,7 +10690,7 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -10621,10 +10707,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10647,17 +10733,17 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10670,7 +10756,7 @@
         <v>20</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>20</v>
@@ -10682,11 +10768,11 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10704,7 +10790,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10716,7 +10802,7 @@
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10725,7 +10811,7 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>20</v>
@@ -10734,7 +10820,7 @@
         <v>20</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>20</v>
@@ -10742,10 +10828,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10768,17 +10854,17 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10791,7 +10877,7 @@
         <v>20</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>20</v>
@@ -10803,13 +10889,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10827,7 +10913,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10839,7 +10925,7 @@
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10848,7 +10934,7 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
@@ -10865,10 +10951,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10891,19 +10977,19 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10952,7 +11038,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10964,7 +11050,7 @@
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10973,7 +11059,7 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -10982,7 +11068,7 @@
         <v>20</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>20</v>
@@ -10990,10 +11076,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11016,19 +11102,19 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11041,7 +11127,7 @@
         <v>20</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>20</v>
@@ -11077,7 +11163,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11089,7 +11175,7 @@
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -11098,7 +11184,7 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>20</v>
@@ -11107,7 +11193,7 @@
         <v>20</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>20</v>
@@ -11115,10 +11201,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11141,19 +11227,19 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11202,7 +11288,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11214,7 +11300,7 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -11223,7 +11309,7 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>20</v>
@@ -11240,10 +11326,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11266,19 +11352,19 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11327,7 +11413,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11339,7 +11425,7 @@
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -11348,7 +11434,7 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>20</v>
@@ -11365,10 +11451,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11391,17 +11477,17 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11414,7 +11500,7 @@
         <v>20</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>20</v>
@@ -11450,7 +11536,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11462,7 +11548,7 @@
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
@@ -11471,7 +11557,7 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>20</v>
@@ -11488,10 +11574,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11514,17 +11600,17 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11573,7 +11659,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11585,7 +11671,7 @@
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11594,7 +11680,7 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>20</v>
@@ -11611,10 +11697,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11637,16 +11723,16 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11672,11 +11758,11 @@
         <v>20</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -11694,7 +11780,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11706,19 +11792,19 @@
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11727,15 +11813,15 @@
         <v>20</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>498</v>
+        <v>518</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11758,16 +11844,16 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11817,7 +11903,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11829,7 +11915,7 @@
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -11838,7 +11924,7 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>20</v>
@@ -11855,10 +11941,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11881,13 +11967,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11938,7 +12024,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11959,7 +12045,7 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>20</v>
@@ -11976,14 +12062,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12002,16 +12088,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12061,7 +12147,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12073,7 +12159,7 @@
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -12082,7 +12168,7 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>20</v>
@@ -12099,14 +12185,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12125,19 +12211,19 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>345</v>
+        <v>177</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12186,7 +12272,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12198,7 +12284,7 @@
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
@@ -12207,7 +12293,7 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>20</v>
@@ -12224,10 +12310,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12250,13 +12336,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12307,7 +12393,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12319,22 +12405,22 @@
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>20</v>
@@ -12345,10 +12431,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12371,16 +12457,16 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12406,13 +12492,13 @@
         <v>20</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -12430,7 +12516,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12442,16 +12528,16 @@
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>20</v>
@@ -12463,15 +12549,15 @@
         <v>20</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>521</v>
+        <v>544</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12494,13 +12580,13 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12551,7 +12637,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12563,19 +12649,19 @@
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12584,15 +12670,15 @@
         <v>20</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>528</v>
+        <v>552</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12615,13 +12701,13 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12672,7 +12758,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12693,7 +12779,7 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>20</v>
@@ -12710,14 +12796,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>283</v>
+        <v>173</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12736,16 +12822,16 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12783,19 +12869,19 @@
         <v>20</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12807,7 +12893,7 @@
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
@@ -12816,7 +12902,7 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>20</v>
@@ -12833,10 +12919,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12859,16 +12945,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12918,7 +13004,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12927,10 +13013,10 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>20</v>
@@ -12939,7 +13025,7 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>20</v>
@@ -12948,7 +13034,7 @@
         <v>20</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>20</v>
@@ -12956,10 +13042,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12982,23 +13068,23 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>542</v>
+        <v>566</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>20</v>
@@ -13043,7 +13129,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13052,10 +13138,10 @@
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
@@ -13064,7 +13150,7 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>20</v>
@@ -13073,7 +13159,7 @@
         <v>20</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>20</v>
@@ -13081,10 +13167,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13107,13 +13193,13 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13140,11 +13226,11 @@
         <v>20</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
@@ -13162,7 +13248,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13174,19 +13260,19 @@
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13195,15 +13281,15 @@
         <v>20</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>553</v>
+        <v>578</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13226,19 +13312,19 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13263,11 +13349,11 @@
         <v>20</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -13285,7 +13371,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13297,19 +13383,19 @@
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13318,15 +13404,15 @@
         <v>20</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>559</v>
+        <v>584</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13349,13 +13435,13 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13406,7 +13492,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13418,19 +13504,19 @@
         <v>20</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13439,15 +13525,15 @@
         <v>20</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>562</v>
+        <v>588</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13470,16 +13556,16 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13529,7 +13615,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13541,19 +13627,19 @@
         <v>20</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
@@ -13562,7 +13648,7 @@
         <v>20</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>570</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
